--- a/Templates/raw_indicators.xlsx
+++ b/Templates/raw_indicators.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aa4c1864c6ba7ffe/Apps/Policy Priority Inference/Templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D17FAE4-2E6B-4B31-92F1-151F6B8AEFE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{1D17FAE4-2E6B-4B31-92F1-151F6B8AEFE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C9EEDAD-30E6-41C9-A5CF-7B030E07BDFF}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$R$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$S$99</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="220">
   <si>
     <t>seriesCode</t>
   </si>
@@ -693,6 +693,9 @@
   </si>
   <si>
     <t>Proporción de las exportaciones dominicanas respecto al Producto Interno Bruto</t>
+  </si>
+  <si>
+    <t>Invert</t>
   </si>
 </sst>
 </file>
@@ -1068,13 +1071,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S99"/>
+  <dimension ref="A1:T99"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="18" max="18" width="11.140625" customWidth="1"/>
+    <col min="19" max="19" width="11.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" s="1">
         <v>2015</v>
       </c>
@@ -1121,16 +1124,19 @@
         <v>1</v>
       </c>
       <c r="P1" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>0.64694444444444343</v>
       </c>
@@ -1176,18 +1182,21 @@
       <c r="O2">
         <v>1</v>
       </c>
-      <c r="P2" t="s">
+      <c r="P2">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="s">
         <v>9</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>10</v>
       </c>
-      <c r="R2">
+      <c r="S2">
         <v>0.85333333333333339</v>
       </c>
-      <c r="S2" s="2"/>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T2" s="2"/>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>0.29557142857142793</v>
       </c>
@@ -1233,18 +1242,21 @@
       <c r="O3">
         <v>1</v>
       </c>
-      <c r="P3" t="s">
+      <c r="P3">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="s">
         <v>12</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="R3" t="s">
         <v>10</v>
       </c>
-      <c r="R3">
+      <c r="S3">
         <v>0.49287000000000003</v>
       </c>
-      <c r="S3" s="2"/>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T3" s="2"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>0.30203888888888741</v>
       </c>
@@ -1290,18 +1302,21 @@
       <c r="O4">
         <v>1</v>
       </c>
-      <c r="P4" t="s">
+      <c r="P4">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="s">
         <v>14</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="R4" t="s">
         <v>10</v>
       </c>
-      <c r="R4">
+      <c r="S4">
         <v>0.7</v>
       </c>
-      <c r="S4" s="2"/>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T4" s="2"/>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>0.32489444444445326</v>
       </c>
@@ -1347,18 +1362,21 @@
       <c r="O5">
         <v>1</v>
       </c>
-      <c r="P5" t="s">
+      <c r="P5">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="s">
         <v>16</v>
       </c>
-      <c r="Q5" t="s">
+      <c r="R5" t="s">
         <v>10</v>
       </c>
-      <c r="R5">
+      <c r="S5">
         <v>0.7</v>
       </c>
-      <c r="S5" s="2"/>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T5" s="2"/>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>0.68939999999999912</v>
       </c>
@@ -1404,18 +1422,21 @@
       <c r="O6">
         <v>1</v>
       </c>
-      <c r="P6" t="s">
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="s">
         <v>18</v>
       </c>
-      <c r="Q6" t="s">
+      <c r="R6" t="s">
         <v>10</v>
       </c>
-      <c r="R6">
+      <c r="S6">
         <v>0.7982571103374394</v>
       </c>
-      <c r="S6" s="2"/>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T6" s="2"/>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>0.50409999999999999</v>
       </c>
@@ -1461,18 +1482,21 @@
       <c r="O7">
         <v>1</v>
       </c>
-      <c r="P7" t="s">
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="s">
         <v>20</v>
       </c>
-      <c r="Q7" t="s">
+      <c r="R7" t="s">
         <v>10</v>
       </c>
-      <c r="R7">
+      <c r="S7">
         <v>0.58079999999999998</v>
       </c>
-      <c r="S7" s="3"/>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T7" s="3"/>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>0.51400000000000001</v>
       </c>
@@ -1518,18 +1542,21 @@
       <c r="O8">
         <v>1</v>
       </c>
-      <c r="P8" t="s">
+      <c r="P8">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="s">
         <v>22</v>
       </c>
-      <c r="Q8" t="s">
+      <c r="R8" t="s">
         <v>23</v>
       </c>
-      <c r="R8">
+      <c r="S8">
         <v>0.58632399999999996</v>
       </c>
-      <c r="S8" s="2"/>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T8" s="2"/>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>0.89430000000000009</v>
       </c>
@@ -1575,18 +1602,21 @@
       <c r="O9">
         <v>1</v>
       </c>
-      <c r="P9" t="s">
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="s">
         <v>25</v>
       </c>
-      <c r="Q9" t="s">
+      <c r="R9" t="s">
         <v>23</v>
       </c>
-      <c r="R9">
+      <c r="S9">
         <v>0.9</v>
       </c>
-      <c r="S9" s="2"/>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T9" s="2"/>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>0.2945714285714286</v>
       </c>
@@ -1632,18 +1662,21 @@
       <c r="O10">
         <v>1</v>
       </c>
-      <c r="P10" t="s">
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="s">
         <v>27</v>
       </c>
-      <c r="Q10" t="s">
+      <c r="R10" t="s">
         <v>23</v>
       </c>
-      <c r="R10">
+      <c r="S10">
         <v>0.39629142857142857</v>
       </c>
-      <c r="S10" s="2"/>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T10" s="2"/>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>0.44170000000000004</v>
       </c>
@@ -1689,18 +1722,21 @@
       <c r="O11">
         <v>1</v>
       </c>
-      <c r="P11" t="s">
+      <c r="P11">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="s">
         <v>29</v>
       </c>
-      <c r="Q11" t="s">
+      <c r="R11" t="s">
         <v>30</v>
       </c>
-      <c r="R11">
+      <c r="S11">
         <v>0.55434499999999998</v>
       </c>
-      <c r="S11" s="2"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T11" s="2"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>0.67879999999999996</v>
       </c>
@@ -1746,18 +1782,21 @@
       <c r="O12">
         <v>1</v>
       </c>
-      <c r="P12" t="s">
+      <c r="P12">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="s">
         <v>32</v>
       </c>
-      <c r="Q12" t="s">
+      <c r="R12" t="s">
         <v>30</v>
       </c>
-      <c r="R12">
+      <c r="S12">
         <v>0.74</v>
       </c>
-      <c r="S12" s="2"/>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T12" s="2"/>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>0.754</v>
       </c>
@@ -1803,18 +1842,21 @@
       <c r="O13">
         <v>1</v>
       </c>
-      <c r="P13" t="s">
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="s">
         <v>34</v>
       </c>
-      <c r="Q13" t="s">
+      <c r="R13" t="s">
         <v>30</v>
       </c>
-      <c r="R13">
+      <c r="S13">
         <v>0.95</v>
       </c>
-      <c r="S13" s="2"/>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T13" s="2"/>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>0.57740000000000002</v>
       </c>
@@ -1860,18 +1902,21 @@
       <c r="O14">
         <v>1</v>
       </c>
-      <c r="P14" t="s">
+      <c r="P14">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="s">
         <v>36</v>
       </c>
-      <c r="Q14" t="s">
+      <c r="R14" t="s">
         <v>30</v>
       </c>
-      <c r="R14">
+      <c r="S14">
         <v>0.673925</v>
       </c>
-      <c r="S14" s="3"/>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T14" s="3"/>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>0.43974999999999997</v>
       </c>
@@ -1917,18 +1962,21 @@
       <c r="O15">
         <v>1</v>
       </c>
-      <c r="P15" t="s">
+      <c r="P15">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="s">
         <v>38</v>
       </c>
-      <c r="Q15" t="s">
+      <c r="R15" t="s">
         <v>30</v>
       </c>
-      <c r="R15">
+      <c r="S15">
         <v>0.62005642583120202</v>
       </c>
-      <c r="S15" s="3"/>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T15" s="3"/>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>0.50700000000000001</v>
       </c>
@@ -1974,18 +2022,21 @@
       <c r="O16">
         <v>1</v>
       </c>
-      <c r="P16" t="s">
+      <c r="P16">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="s">
         <v>40</v>
       </c>
-      <c r="Q16" t="s">
+      <c r="R16" t="s">
         <v>30</v>
       </c>
-      <c r="R16">
+      <c r="S16">
         <v>0.878</v>
       </c>
-      <c r="S16" s="2"/>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T16" s="2"/>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>0.33374999999999999</v>
       </c>
@@ -2031,18 +2082,21 @@
       <c r="O17">
         <v>1</v>
       </c>
-      <c r="P17" t="s">
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="s">
         <v>42</v>
       </c>
-      <c r="Q17" t="s">
+      <c r="R17" t="s">
         <v>30</v>
       </c>
-      <c r="R17">
+      <c r="S17">
         <v>0.55125000000000002</v>
       </c>
-      <c r="S17" s="3"/>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T17" s="3"/>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>0.72599999999999998</v>
       </c>
@@ -2088,18 +2142,21 @@
       <c r="O18">
         <v>1</v>
       </c>
-      <c r="P18" t="s">
+      <c r="P18">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="s">
         <v>44</v>
       </c>
-      <c r="Q18" t="s">
+      <c r="R18" t="s">
         <v>30</v>
       </c>
-      <c r="R18">
+      <c r="S18">
         <v>0.70829799999999998</v>
       </c>
-      <c r="S18" s="3"/>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T18" s="3"/>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>0.72066666666666657</v>
       </c>
@@ -2145,18 +2202,21 @@
       <c r="O19">
         <v>0</v>
       </c>
-      <c r="P19" t="s">
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="s">
         <v>46</v>
       </c>
-      <c r="Q19" t="s">
+      <c r="R19" t="s">
         <v>30</v>
       </c>
-      <c r="R19">
+      <c r="S19">
         <v>0.78333333333333333</v>
       </c>
-      <c r="S19" s="2"/>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T19" s="2"/>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>0.50249537037036873</v>
       </c>
@@ -2202,18 +2262,21 @@
       <c r="O20">
         <v>1</v>
       </c>
-      <c r="P20" t="s">
+      <c r="P20">
+        <v>1</v>
+      </c>
+      <c r="Q20" t="s">
         <v>48</v>
       </c>
-      <c r="Q20" t="s">
+      <c r="R20" t="s">
         <v>30</v>
       </c>
-      <c r="R20">
+      <c r="S20">
         <v>0.59249999999999992</v>
       </c>
-      <c r="S20" s="3"/>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T20" s="3"/>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>0.66689999999999994</v>
       </c>
@@ -2259,18 +2322,21 @@
       <c r="O21">
         <v>1</v>
       </c>
-      <c r="P21" t="s">
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="s">
         <v>50</v>
       </c>
-      <c r="Q21" t="s">
+      <c r="R21" t="s">
         <v>30</v>
       </c>
-      <c r="R21">
+      <c r="S21">
         <v>0.99</v>
       </c>
-      <c r="S21" s="3"/>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T21" s="3"/>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>0.75700000000000001</v>
       </c>
@@ -2316,18 +2382,21 @@
       <c r="O22">
         <v>1</v>
       </c>
-      <c r="P22" t="s">
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="s">
         <v>52</v>
       </c>
-      <c r="Q22" t="s">
+      <c r="R22" t="s">
         <v>30</v>
       </c>
-      <c r="R22">
+      <c r="S22">
         <v>0.91459999999999997</v>
       </c>
-      <c r="S22" s="3"/>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T22" s="3"/>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>0.7998412698412698</v>
       </c>
@@ -2373,18 +2442,21 @@
       <c r="O23">
         <v>1</v>
       </c>
-      <c r="P23" t="s">
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="s">
         <v>54</v>
       </c>
-      <c r="Q23" t="s">
+      <c r="R23" t="s">
         <v>55</v>
       </c>
-      <c r="R23">
+      <c r="S23">
         <v>0.97051857142857145</v>
       </c>
-      <c r="S23" s="2"/>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T23" s="2"/>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>0.67923076923077019</v>
       </c>
@@ -2430,18 +2502,21 @@
       <c r="O24">
         <v>1</v>
       </c>
-      <c r="P24" t="s">
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="s">
         <v>57</v>
       </c>
-      <c r="Q24" t="s">
+      <c r="R24" t="s">
         <v>55</v>
       </c>
-      <c r="R24">
+      <c r="S24">
         <v>0.93550769230769226</v>
       </c>
-      <c r="S24" s="2"/>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T24" s="2"/>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>0.6542</v>
       </c>
@@ -2487,18 +2562,21 @@
       <c r="O25">
         <v>1</v>
       </c>
-      <c r="P25" t="s">
+      <c r="P25">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="s">
         <v>59</v>
       </c>
-      <c r="Q25" t="s">
+      <c r="R25" t="s">
         <v>55</v>
       </c>
-      <c r="R25">
+      <c r="S25">
         <v>0.45490699999999995</v>
       </c>
-      <c r="S25" s="2"/>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T25" s="2"/>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>0.60333333333333339</v>
       </c>
@@ -2544,18 +2622,21 @@
       <c r="O26">
         <v>1</v>
       </c>
-      <c r="P26" t="s">
+      <c r="P26">
+        <v>1</v>
+      </c>
+      <c r="Q26" t="s">
         <v>61</v>
       </c>
-      <c r="Q26" t="s">
+      <c r="R26" t="s">
         <v>55</v>
       </c>
-      <c r="R26">
+      <c r="S26">
         <v>0.89062133333333338</v>
       </c>
-      <c r="S26" s="2"/>
-    </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T26" s="2"/>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>0.46333333333333326</v>
       </c>
@@ -2601,18 +2682,21 @@
       <c r="O27">
         <v>1</v>
       </c>
-      <c r="P27" t="s">
+      <c r="P27">
+        <v>1</v>
+      </c>
+      <c r="Q27" t="s">
         <v>63</v>
       </c>
-      <c r="Q27" t="s">
+      <c r="R27" t="s">
         <v>55</v>
       </c>
-      <c r="R27">
+      <c r="S27">
         <v>0.82283533333333336</v>
       </c>
-      <c r="S27" s="2"/>
-    </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T27" s="2"/>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>0.93799999999999994</v>
       </c>
@@ -2658,18 +2742,21 @@
       <c r="O28">
         <v>1</v>
       </c>
-      <c r="P28" t="s">
+      <c r="P28">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="s">
         <v>65</v>
       </c>
-      <c r="Q28" t="s">
+      <c r="R28" t="s">
         <v>55</v>
       </c>
-      <c r="R28">
+      <c r="S28">
         <v>0.94448800000000011</v>
       </c>
-      <c r="S28" s="2"/>
-    </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T28" s="2"/>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>0.59</v>
       </c>
@@ -2715,18 +2802,21 @@
       <c r="O29">
         <v>1</v>
       </c>
-      <c r="P29" t="s">
+      <c r="P29">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="s">
         <v>67</v>
       </c>
-      <c r="Q29" t="s">
+      <c r="R29" t="s">
         <v>55</v>
       </c>
-      <c r="R29">
+      <c r="S29">
         <v>0.89019999999999999</v>
       </c>
-      <c r="S29" s="2"/>
-    </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T29" s="2"/>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>0.46566666666666379</v>
       </c>
@@ -2772,18 +2862,21 @@
       <c r="O30">
         <v>1</v>
       </c>
-      <c r="P30" t="s">
+      <c r="P30">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="s">
         <v>69</v>
       </c>
-      <c r="Q30" t="s">
+      <c r="R30" t="s">
         <v>55</v>
       </c>
-      <c r="R30">
+      <c r="S30">
         <v>0.69499999999999995</v>
       </c>
-      <c r="S30" s="2"/>
-    </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T30" s="2"/>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>0.21902777777777871</v>
       </c>
@@ -2829,18 +2922,21 @@
       <c r="O31">
         <v>1</v>
       </c>
-      <c r="P31" t="s">
+      <c r="P31">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="s">
         <v>71</v>
       </c>
-      <c r="Q31" t="s">
+      <c r="R31" t="s">
         <v>55</v>
       </c>
-      <c r="R31">
+      <c r="S31">
         <v>0.35</v>
       </c>
-      <c r="S31" s="2"/>
-    </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T31" s="2"/>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>0.95871428571428585</v>
       </c>
@@ -2886,18 +2982,21 @@
       <c r="O32">
         <v>1</v>
       </c>
-      <c r="P32" t="s">
+      <c r="P32">
+        <v>1</v>
+      </c>
+      <c r="Q32" t="s">
         <v>73</v>
       </c>
-      <c r="Q32" t="s">
+      <c r="R32" t="s">
         <v>55</v>
       </c>
-      <c r="R32">
+      <c r="S32">
         <v>0.96</v>
       </c>
-      <c r="S32" s="2"/>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T32" s="2"/>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>0.92099999999999937</v>
       </c>
@@ -2943,18 +3042,21 @@
       <c r="O33">
         <v>1</v>
       </c>
-      <c r="P33" t="s">
+      <c r="P33">
+        <v>1</v>
+      </c>
+      <c r="Q33" t="s">
         <v>75</v>
       </c>
-      <c r="Q33" t="s">
+      <c r="R33" t="s">
         <v>55</v>
       </c>
-      <c r="R33">
+      <c r="S33">
         <v>0.91200000000000003</v>
       </c>
-      <c r="S33" s="2"/>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T33" s="2"/>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>6.6600000000000006E-2</v>
       </c>
@@ -3000,18 +3102,21 @@
       <c r="O34">
         <v>1</v>
       </c>
-      <c r="P34" t="s">
+      <c r="P34">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="s">
         <v>77</v>
       </c>
-      <c r="Q34" t="s">
+      <c r="R34" t="s">
         <v>55</v>
       </c>
-      <c r="R34">
+      <c r="S34">
         <v>0.38627600000000001</v>
       </c>
-      <c r="S34" s="2"/>
-    </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T34" s="2"/>
+    </row>
+    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>0.46799999999999997</v>
       </c>
@@ -3057,18 +3162,21 @@
       <c r="O35">
         <v>1</v>
       </c>
-      <c r="P35" t="s">
+      <c r="P35">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="s">
         <v>79</v>
       </c>
-      <c r="Q35" t="s">
+      <c r="R35" t="s">
         <v>55</v>
       </c>
-      <c r="R35">
+      <c r="S35">
         <v>0.90790000000000004</v>
       </c>
-      <c r="S35" s="2"/>
-    </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T35" s="2"/>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>8.7250000000000008E-2</v>
       </c>
@@ -3114,18 +3222,21 @@
       <c r="O36">
         <v>1</v>
       </c>
-      <c r="P36" t="s">
+      <c r="P36">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="s">
         <v>81</v>
       </c>
-      <c r="Q36" t="s">
+      <c r="R36" t="s">
         <v>55</v>
       </c>
-      <c r="R36">
+      <c r="S36">
         <v>0.50049999999999994</v>
       </c>
-      <c r="S36" s="2"/>
-    </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T36" s="2"/>
+    </row>
+    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>0.20585714285714474</v>
       </c>
@@ -3171,18 +3282,21 @@
       <c r="O37">
         <v>1</v>
       </c>
-      <c r="P37" t="s">
+      <c r="P37">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="s">
         <v>83</v>
       </c>
-      <c r="Q37" t="s">
+      <c r="R37" t="s">
         <v>55</v>
       </c>
-      <c r="R37">
+      <c r="S37">
         <v>0.53239999999999998</v>
       </c>
-      <c r="S37" s="2"/>
-    </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T37" s="2"/>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>0.41333333333333333</v>
       </c>
@@ -3228,18 +3342,21 @@
       <c r="O38">
         <v>1</v>
       </c>
-      <c r="P38" t="s">
+      <c r="P38">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="s">
         <v>85</v>
       </c>
-      <c r="Q38" t="s">
+      <c r="R38" t="s">
         <v>55</v>
       </c>
-      <c r="R38">
+      <c r="S38">
         <v>0.43240666666666672</v>
       </c>
-      <c r="S38" s="2"/>
-    </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T38" s="2"/>
+    </row>
+    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>0.75760000000000005</v>
       </c>
@@ -3285,18 +3402,21 @@
       <c r="O39">
         <v>1</v>
       </c>
-      <c r="P39" t="s">
+      <c r="P39">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="s">
         <v>87</v>
       </c>
-      <c r="Q39" t="s">
+      <c r="R39" t="s">
         <v>55</v>
       </c>
-      <c r="R39">
+      <c r="S39">
         <v>0.79239999999999999</v>
       </c>
-      <c r="S39" s="2"/>
-    </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T39" s="2"/>
+    </row>
+    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>0.46666666666666667</v>
       </c>
@@ -3342,18 +3462,21 @@
       <c r="O40">
         <v>1</v>
       </c>
-      <c r="P40" t="s">
+      <c r="P40">
+        <v>1</v>
+      </c>
+      <c r="Q40" t="s">
         <v>89</v>
       </c>
-      <c r="Q40" t="s">
+      <c r="R40" t="s">
         <v>55</v>
       </c>
-      <c r="R40">
+      <c r="S40">
         <v>0.65533333333333332</v>
       </c>
-      <c r="S40" s="2"/>
-    </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T40" s="2"/>
+    </row>
+    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>0.28050000000000003</v>
       </c>
@@ -3399,18 +3522,21 @@
       <c r="O41">
         <v>1</v>
       </c>
-      <c r="P41" t="s">
+      <c r="P41">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="s">
         <v>91</v>
       </c>
-      <c r="Q41" t="s">
+      <c r="R41" t="s">
         <v>55</v>
       </c>
-      <c r="R41">
+      <c r="S41">
         <v>0.24120349999999999</v>
       </c>
-      <c r="S41" s="2"/>
-    </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T41" s="2"/>
+    </row>
+    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>0.27250000000000002</v>
       </c>
@@ -3456,18 +3582,21 @@
       <c r="O42">
         <v>1</v>
       </c>
-      <c r="P42" t="s">
+      <c r="P42">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="s">
         <v>93</v>
       </c>
-      <c r="Q42" t="s">
+      <c r="R42" t="s">
         <v>55</v>
       </c>
-      <c r="R42">
+      <c r="S42">
         <v>0.45320099999999996</v>
       </c>
-      <c r="S42" s="2"/>
-    </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T42" s="2"/>
+    </row>
+    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>0.1865</v>
       </c>
@@ -3513,18 +3642,21 @@
       <c r="O43">
         <v>1</v>
       </c>
-      <c r="P43" t="s">
+      <c r="P43">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="s">
         <v>95</v>
       </c>
-      <c r="Q43" t="s">
+      <c r="R43" t="s">
         <v>55</v>
       </c>
-      <c r="R43">
+      <c r="S43">
         <v>0.206155</v>
       </c>
-      <c r="S43" s="2"/>
-    </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T43" s="2"/>
+    </row>
+    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>0.74</v>
       </c>
@@ -3570,18 +3702,21 @@
       <c r="O44">
         <v>1</v>
       </c>
-      <c r="P44" t="s">
+      <c r="P44">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="s">
         <v>97</v>
       </c>
-      <c r="Q44" t="s">
+      <c r="R44" t="s">
         <v>98</v>
       </c>
-      <c r="R44">
+      <c r="S44">
         <v>0.81884000000000001</v>
       </c>
-      <c r="S44" s="2"/>
-    </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T44" s="2"/>
+    </row>
+    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>0.5675</v>
       </c>
@@ -3627,18 +3762,21 @@
       <c r="O45">
         <v>1</v>
       </c>
-      <c r="P45" t="s">
+      <c r="P45">
+        <v>1</v>
+      </c>
+      <c r="Q45" t="s">
         <v>100</v>
       </c>
-      <c r="Q45" t="s">
+      <c r="R45" t="s">
         <v>98</v>
       </c>
-      <c r="R45">
+      <c r="S45">
         <v>0.75541000000000003</v>
       </c>
-      <c r="S45" s="3"/>
-    </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T45" s="3"/>
+    </row>
+    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>0.93220000000000003</v>
       </c>
@@ -3684,18 +3822,21 @@
       <c r="O46">
         <v>1</v>
       </c>
-      <c r="P46" t="s">
+      <c r="P46">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="s">
         <v>102</v>
       </c>
-      <c r="Q46" t="s">
+      <c r="R46" t="s">
         <v>103</v>
       </c>
-      <c r="R46">
+      <c r="S46">
         <v>0.95</v>
       </c>
-      <c r="S46" s="3"/>
-    </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T46" s="3"/>
+    </row>
+    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>0.84299999999999997</v>
       </c>
@@ -3741,18 +3882,21 @@
       <c r="O47">
         <v>1</v>
       </c>
-      <c r="P47" t="s">
+      <c r="P47">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="s">
         <v>105</v>
       </c>
-      <c r="Q47" t="s">
+      <c r="R47" t="s">
         <v>103</v>
       </c>
-      <c r="R47">
+      <c r="S47">
         <v>0.94010000000000005</v>
       </c>
-      <c r="S47" s="2"/>
-    </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T47" s="2"/>
+    </row>
+    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>0.62437222222222388</v>
       </c>
@@ -3798,18 +3942,21 @@
       <c r="O48">
         <v>1</v>
       </c>
-      <c r="P48" t="s">
+      <c r="P48">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="s">
         <v>107</v>
       </c>
-      <c r="Q48" t="s">
+      <c r="R48" t="s">
         <v>103</v>
       </c>
-      <c r="R48">
+      <c r="S48">
         <v>0.72527799999999998</v>
       </c>
-      <c r="S48" s="2"/>
-    </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T48" s="2"/>
+    </row>
+    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>0.8567555555555556</v>
       </c>
@@ -3855,18 +4002,21 @@
       <c r="O49">
         <v>1</v>
       </c>
-      <c r="P49" t="s">
+      <c r="P49">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="s">
         <v>109</v>
       </c>
-      <c r="Q49" t="s">
+      <c r="R49" t="s">
         <v>103</v>
       </c>
-      <c r="R49">
+      <c r="S49">
         <v>0.77777777777777779</v>
       </c>
-      <c r="S49" s="2"/>
-    </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T49" s="2"/>
+    </row>
+    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>0.3044</v>
       </c>
@@ -3912,18 +4062,21 @@
       <c r="O50">
         <v>1</v>
       </c>
-      <c r="P50" t="s">
+      <c r="P50">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="s">
         <v>111</v>
       </c>
-      <c r="Q50" t="s">
+      <c r="R50" t="s">
         <v>103</v>
       </c>
-      <c r="R50">
+      <c r="S50">
         <v>0.45695999999999998</v>
       </c>
-      <c r="S50" s="2"/>
-    </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T50" s="2"/>
+    </row>
+    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>0.24871944444444472</v>
       </c>
@@ -3969,18 +4122,21 @@
       <c r="O51">
         <v>1</v>
       </c>
-      <c r="P51" t="s">
+      <c r="P51">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="s">
         <v>113</v>
       </c>
-      <c r="Q51" t="s">
+      <c r="R51" t="s">
         <v>103</v>
       </c>
-      <c r="R51">
+      <c r="S51">
         <v>0.26739999999999997</v>
       </c>
-      <c r="S51" s="2"/>
-    </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T51" s="2"/>
+    </row>
+    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>0.12279999999999999</v>
       </c>
@@ -4026,18 +4182,21 @@
       <c r="O52">
         <v>1</v>
       </c>
-      <c r="P52" t="s">
+      <c r="P52">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="s">
         <v>115</v>
       </c>
-      <c r="Q52" t="s">
+      <c r="R52" t="s">
         <v>103</v>
       </c>
-      <c r="R52">
+      <c r="S52">
         <v>0.21720000000000003</v>
       </c>
-      <c r="S52" s="2"/>
-    </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T52" s="2"/>
+    </row>
+    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>0.32999999999999996</v>
       </c>
@@ -4083,18 +4242,21 @@
       <c r="O53">
         <v>1</v>
       </c>
-      <c r="P53" t="s">
+      <c r="P53">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="s">
         <v>117</v>
       </c>
-      <c r="Q53" t="s">
+      <c r="R53" t="s">
         <v>118</v>
       </c>
-      <c r="R53">
+      <c r="S53">
         <v>0.5</v>
       </c>
-      <c r="S53" s="2"/>
-    </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T53" s="2"/>
+    </row>
+    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>0.16440000000000002</v>
       </c>
@@ -4140,18 +4302,21 @@
       <c r="O54">
         <v>1</v>
       </c>
-      <c r="P54" t="s">
+      <c r="P54">
+        <v>1</v>
+      </c>
+      <c r="Q54" t="s">
         <v>120</v>
       </c>
-      <c r="Q54" t="s">
+      <c r="R54" t="s">
         <v>118</v>
       </c>
-      <c r="R54">
+      <c r="S54">
         <v>0.42123299999999997</v>
       </c>
-      <c r="S54" s="2"/>
-    </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T54" s="2"/>
+    </row>
+    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>0.55642857142857149</v>
       </c>
@@ -4197,18 +4362,21 @@
       <c r="O55">
         <v>1</v>
       </c>
-      <c r="P55" t="s">
+      <c r="P55">
+        <v>1</v>
+      </c>
+      <c r="Q55" t="s">
         <v>122</v>
       </c>
-      <c r="Q55" t="s">
+      <c r="R55" t="s">
         <v>118</v>
       </c>
-      <c r="R55">
+      <c r="S55">
         <v>0.62857142857142856</v>
       </c>
-      <c r="S55" s="2"/>
-    </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T55" s="2"/>
+    </row>
+    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>0.39550000000000002</v>
       </c>
@@ -4254,18 +4422,21 @@
       <c r="O56">
         <v>0</v>
       </c>
-      <c r="P56" t="s">
+      <c r="P56">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="s">
         <v>124</v>
       </c>
-      <c r="Q56" t="s">
+      <c r="R56" t="s">
         <v>125</v>
       </c>
-      <c r="R56">
+      <c r="S56">
         <v>0.83333333333333337</v>
       </c>
-      <c r="S56" s="2"/>
-    </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T56" s="2"/>
+    </row>
+    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>0.60221333333333338</v>
       </c>
@@ -4311,18 +4482,21 @@
       <c r="O57">
         <v>1</v>
       </c>
-      <c r="P57" t="s">
+      <c r="P57">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="s">
         <v>127</v>
       </c>
-      <c r="Q57" t="s">
+      <c r="R57" t="s">
         <v>125</v>
       </c>
-      <c r="R57">
+      <c r="S57">
         <v>0.89006666666666667</v>
       </c>
-      <c r="S57" s="2"/>
-    </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T57" s="2"/>
+    </row>
+    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>0.471857626364594</v>
       </c>
@@ -4368,18 +4542,21 @@
       <c r="O58">
         <v>1</v>
       </c>
-      <c r="P58" t="s">
+      <c r="P58">
+        <v>1</v>
+      </c>
+      <c r="Q58" t="s">
         <v>129</v>
       </c>
-      <c r="Q58" t="s">
+      <c r="R58" t="s">
         <v>125</v>
       </c>
-      <c r="R58">
+      <c r="S58">
         <v>0.59129031532610421</v>
       </c>
-      <c r="S58" s="2"/>
-    </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T58" s="2"/>
+    </row>
+    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>0.52350000000000008</v>
       </c>
@@ -4425,18 +4602,21 @@
       <c r="O59">
         <v>1</v>
       </c>
-      <c r="P59" t="s">
+      <c r="P59">
+        <v>1</v>
+      </c>
+      <c r="Q59" t="s">
         <v>131</v>
       </c>
-      <c r="Q59" t="s">
+      <c r="R59" t="s">
         <v>125</v>
       </c>
-      <c r="R59">
+      <c r="S59">
         <v>0.69385949999999996</v>
       </c>
-      <c r="S59" s="2"/>
-    </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T59" s="2"/>
+    </row>
+    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>0.56781666666666664</v>
       </c>
@@ -4482,18 +4662,21 @@
       <c r="O60">
         <v>0</v>
       </c>
-      <c r="P60" t="s">
+      <c r="P60">
+        <v>0</v>
+      </c>
+      <c r="Q60" t="s">
         <v>133</v>
       </c>
-      <c r="Q60" t="s">
+      <c r="R60" t="s">
         <v>125</v>
       </c>
-      <c r="R60">
+      <c r="S60">
         <v>0.59079999999999999</v>
       </c>
-      <c r="S60" s="2"/>
-    </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T60" s="2"/>
+    </row>
+    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>0.50106666666666677</v>
       </c>
@@ -4539,18 +4722,21 @@
       <c r="O61">
         <v>0</v>
       </c>
-      <c r="P61" t="s">
+      <c r="P61">
+        <v>0</v>
+      </c>
+      <c r="Q61" t="s">
         <v>135</v>
       </c>
-      <c r="Q61" t="s">
+      <c r="R61" t="s">
         <v>125</v>
       </c>
-      <c r="R61">
+      <c r="S61">
         <v>0.51700000000000002</v>
       </c>
-      <c r="S61" s="2"/>
-    </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T61" s="2"/>
+    </row>
+    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>0.68063888888888791</v>
       </c>
@@ -4596,18 +4782,21 @@
       <c r="O62">
         <v>1</v>
       </c>
-      <c r="P62" t="s">
+      <c r="P62">
+        <v>1</v>
+      </c>
+      <c r="Q62" t="s">
         <v>137</v>
       </c>
-      <c r="Q62" t="s">
+      <c r="R62" t="s">
         <v>125</v>
       </c>
-      <c r="R62">
+      <c r="S62">
         <v>0.83789036375239301</v>
       </c>
-      <c r="S62" s="2"/>
-    </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T62" s="2"/>
+    </row>
+    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>0.83863268581406469</v>
       </c>
@@ -4653,18 +4842,21 @@
       <c r="O63">
         <v>1</v>
       </c>
-      <c r="P63" t="s">
+      <c r="P63">
+        <v>1</v>
+      </c>
+      <c r="Q63" t="s">
         <v>139</v>
       </c>
-      <c r="Q63" t="s">
+      <c r="R63" t="s">
         <v>125</v>
       </c>
-      <c r="R63">
+      <c r="S63">
         <v>0.87351438915043811</v>
       </c>
-      <c r="S63" s="2"/>
-    </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T63" s="2"/>
+    </row>
+    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>0.47939999999999999</v>
       </c>
@@ -4710,18 +4902,21 @@
       <c r="O64">
         <v>0</v>
       </c>
-      <c r="P64" t="s">
+      <c r="P64">
+        <v>0</v>
+      </c>
+      <c r="Q64" t="s">
         <v>141</v>
       </c>
-      <c r="Q64" t="s">
+      <c r="R64" t="s">
         <v>125</v>
       </c>
-      <c r="R64">
+      <c r="S64">
         <v>0.46500000000000002</v>
       </c>
-      <c r="S64" s="2"/>
-    </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T64" s="2"/>
+    </row>
+    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>0.43671944444444399</v>
       </c>
@@ -4767,18 +4962,21 @@
       <c r="O65">
         <v>1</v>
       </c>
-      <c r="P65" t="s">
+      <c r="P65">
+        <v>0</v>
+      </c>
+      <c r="Q65" t="s">
         <v>143</v>
       </c>
-      <c r="Q65" t="s">
+      <c r="R65" t="s">
         <v>125</v>
       </c>
-      <c r="R65">
+      <c r="S65">
         <v>0.52100000000000002</v>
       </c>
-      <c r="S65" s="2"/>
-    </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T65" s="2"/>
+    </row>
+    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>0.74588611111111114</v>
       </c>
@@ -4824,18 +5022,21 @@
       <c r="O66">
         <v>1</v>
       </c>
-      <c r="P66" t="s">
+      <c r="P66">
+        <v>1</v>
+      </c>
+      <c r="Q66" t="s">
         <v>145</v>
       </c>
-      <c r="Q66" t="s">
+      <c r="R66" t="s">
         <v>125</v>
       </c>
-      <c r="R66">
+      <c r="S66">
         <v>0.77894187612208254</v>
       </c>
-      <c r="S66" s="2"/>
-    </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T66" s="2"/>
+    </row>
+    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>0.7713277777777785</v>
       </c>
@@ -4881,18 +5082,21 @@
       <c r="O67">
         <v>1</v>
       </c>
-      <c r="P67" t="s">
+      <c r="P67">
+        <v>1</v>
+      </c>
+      <c r="Q67" t="s">
         <v>147</v>
       </c>
-      <c r="Q67" t="s">
+      <c r="R67" t="s">
         <v>125</v>
       </c>
-      <c r="R67">
+      <c r="S67">
         <v>0.81060367454068238</v>
       </c>
-      <c r="S67" s="2"/>
-    </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T67" s="2"/>
+    </row>
+    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>0.54659999999999997</v>
       </c>
@@ -4938,18 +5142,21 @@
       <c r="O68">
         <v>0</v>
       </c>
-      <c r="P68" t="s">
+      <c r="P68">
+        <v>0</v>
+      </c>
+      <c r="Q68" t="s">
         <v>149</v>
       </c>
-      <c r="Q68" t="s">
+      <c r="R68" t="s">
         <v>125</v>
       </c>
-      <c r="R68">
+      <c r="S68">
         <v>0.75</v>
       </c>
-      <c r="S68" s="2"/>
-    </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T68" s="2"/>
+    </row>
+    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>0.13224975</v>
       </c>
@@ -4995,18 +5202,21 @@
       <c r="O69">
         <v>1</v>
       </c>
-      <c r="P69" t="s">
+      <c r="P69">
+        <v>0</v>
+      </c>
+      <c r="Q69" t="s">
         <v>151</v>
       </c>
-      <c r="Q69" t="s">
+      <c r="R69" t="s">
         <v>125</v>
       </c>
-      <c r="R69">
+      <c r="S69">
         <v>0.7</v>
       </c>
-      <c r="S69" s="2"/>
-    </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T69" s="2"/>
+    </row>
+    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>0.46665491666666664</v>
       </c>
@@ -5052,18 +5262,21 @@
       <c r="O70">
         <v>1</v>
       </c>
-      <c r="P70" t="s">
+      <c r="P70">
+        <v>0</v>
+      </c>
+      <c r="Q70" t="s">
         <v>153</v>
       </c>
-      <c r="Q70" t="s">
+      <c r="R70" t="s">
         <v>125</v>
       </c>
-      <c r="R70">
+      <c r="S70">
         <v>0.74379297666666677</v>
       </c>
-      <c r="S70" s="2"/>
-    </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T70" s="2"/>
+    </row>
+    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>0.13438</v>
       </c>
@@ -5109,18 +5322,21 @@
       <c r="O71">
         <v>0</v>
       </c>
-      <c r="P71" t="s">
+      <c r="P71">
+        <v>0</v>
+      </c>
+      <c r="Q71" t="s">
         <v>155</v>
       </c>
-      <c r="Q71" t="s">
+      <c r="R71" t="s">
         <v>125</v>
       </c>
-      <c r="R71">
+      <c r="S71">
         <v>0.96919999999999995</v>
       </c>
-      <c r="S71" s="2"/>
-    </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T71" s="2"/>
+    </row>
+    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>0.7551000000000001</v>
       </c>
@@ -5166,18 +5382,21 @@
       <c r="O72">
         <v>1</v>
       </c>
-      <c r="P72" t="s">
+      <c r="P72">
+        <v>0</v>
+      </c>
+      <c r="Q72" t="s">
         <v>157</v>
       </c>
-      <c r="Q72" t="s">
+      <c r="R72" t="s">
         <v>125</v>
       </c>
-      <c r="R72">
+      <c r="S72">
         <v>0.78050399999999998</v>
       </c>
-      <c r="S72" s="2"/>
-    </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T72" s="2"/>
+    </row>
+    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>0.73499999999999999</v>
       </c>
@@ -5223,18 +5442,21 @@
       <c r="O73">
         <v>0</v>
       </c>
-      <c r="P73" t="s">
+      <c r="P73">
+        <v>0</v>
+      </c>
+      <c r="Q73" t="s">
         <v>159</v>
       </c>
-      <c r="Q73" t="s">
+      <c r="R73" t="s">
         <v>160</v>
       </c>
-      <c r="R73">
+      <c r="S73">
         <v>0.79664400000000002</v>
       </c>
-      <c r="S73" s="2"/>
-    </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T73" s="2"/>
+    </row>
+    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>0.53714285714285714</v>
       </c>
@@ -5280,18 +5502,21 @@
       <c r="O74">
         <v>1</v>
       </c>
-      <c r="P74" t="s">
+      <c r="P74">
+        <v>0</v>
+      </c>
+      <c r="Q74" t="s">
         <v>162</v>
       </c>
-      <c r="Q74" t="s">
+      <c r="R74" t="s">
         <v>160</v>
       </c>
-      <c r="R74">
+      <c r="S74">
         <v>0.66787714285714284</v>
       </c>
-      <c r="S74" s="2"/>
-    </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T74" s="2"/>
+    </row>
+    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>0.27</v>
       </c>
@@ -5337,18 +5562,21 @@
       <c r="O75">
         <v>0</v>
       </c>
-      <c r="P75" t="s">
+      <c r="P75">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="s">
         <v>164</v>
       </c>
-      <c r="Q75" t="s">
+      <c r="R75" t="s">
         <v>160</v>
       </c>
-      <c r="R75">
+      <c r="S75">
         <v>0.84099999999999997</v>
       </c>
-      <c r="S75" s="2"/>
-    </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T75" s="2"/>
+    </row>
+    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>0.49459999999999998</v>
       </c>
@@ -5394,18 +5622,21 @@
       <c r="O76">
         <v>1</v>
       </c>
-      <c r="P76" t="s">
+      <c r="P76">
+        <v>0</v>
+      </c>
+      <c r="Q76" t="s">
         <v>166</v>
       </c>
-      <c r="Q76" t="s">
+      <c r="R76" t="s">
         <v>167</v>
       </c>
-      <c r="R76">
+      <c r="S76">
         <v>0.5</v>
       </c>
-      <c r="S76" s="3"/>
-    </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T76" s="3"/>
+    </row>
+    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>0.52967727272727272</v>
       </c>
@@ -5451,18 +5682,21 @@
       <c r="O77">
         <v>1</v>
       </c>
-      <c r="P77" t="s">
+      <c r="P77">
+        <v>0</v>
+      </c>
+      <c r="Q77" t="s">
         <v>169</v>
       </c>
-      <c r="Q77" t="s">
+      <c r="R77" t="s">
         <v>167</v>
       </c>
-      <c r="R77">
+      <c r="S77">
         <v>0.78433225646619142</v>
       </c>
-      <c r="S77" s="3"/>
-    </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T77" s="3"/>
+    </row>
+    <row r="78" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>0.366458333333334</v>
       </c>
@@ -5508,18 +5742,21 @@
       <c r="O78">
         <v>1</v>
       </c>
-      <c r="P78" t="s">
+      <c r="P78">
+        <v>1</v>
+      </c>
+      <c r="Q78" t="s">
         <v>171</v>
       </c>
-      <c r="Q78" t="s">
+      <c r="R78" t="s">
         <v>172</v>
       </c>
-      <c r="R78">
+      <c r="S78">
         <v>0.5665</v>
       </c>
-      <c r="S78" s="2"/>
-    </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T78" s="2"/>
+    </row>
+    <row r="79" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>0.43897222222222254</v>
       </c>
@@ -5565,18 +5802,21 @@
       <c r="O79">
         <v>1</v>
       </c>
-      <c r="P79" t="s">
+      <c r="P79">
+        <v>1</v>
+      </c>
+      <c r="Q79" t="s">
         <v>174</v>
       </c>
-      <c r="Q79" t="s">
+      <c r="R79" t="s">
         <v>172</v>
       </c>
-      <c r="R79">
+      <c r="S79">
         <v>0.65437100000000004</v>
       </c>
-      <c r="S79" s="2"/>
-    </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T79" s="2"/>
+    </row>
+    <row r="80" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>0.52628571428571469</v>
       </c>
@@ -5622,18 +5862,21 @@
       <c r="O80">
         <v>0</v>
       </c>
-      <c r="P80" t="s">
+      <c r="P80">
+        <v>0</v>
+      </c>
+      <c r="Q80" t="s">
         <v>176</v>
       </c>
-      <c r="Q80" t="s">
+      <c r="R80" t="s">
         <v>172</v>
       </c>
-      <c r="R80">
+      <c r="S80">
         <v>0.61258199999999996</v>
       </c>
-      <c r="S80" s="2"/>
-    </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T80" s="2"/>
+    </row>
+    <row r="81" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>0.26316666666666666</v>
       </c>
@@ -5679,18 +5922,21 @@
       <c r="O81">
         <v>1</v>
       </c>
-      <c r="P81" t="s">
+      <c r="P81">
+        <v>1</v>
+      </c>
+      <c r="Q81" t="s">
         <v>178</v>
       </c>
-      <c r="Q81" t="s">
+      <c r="R81" t="s">
         <v>172</v>
       </c>
-      <c r="R81">
+      <c r="S81">
         <v>0.4217866666666667</v>
       </c>
-      <c r="S81" s="2"/>
-    </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T81" s="2"/>
+    </row>
+    <row r="82" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>0.21050000000000005</v>
       </c>
@@ -5736,18 +5982,21 @@
       <c r="O82">
         <v>1</v>
       </c>
-      <c r="P82" t="s">
+      <c r="P82">
+        <v>1</v>
+      </c>
+      <c r="Q82" t="s">
         <v>180</v>
       </c>
-      <c r="Q82" t="s">
+      <c r="R82" t="s">
         <v>172</v>
       </c>
-      <c r="R82">
+      <c r="S82">
         <v>0.39373250000000004</v>
       </c>
-      <c r="S82" s="2"/>
-    </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T82" s="2"/>
+    </row>
+    <row r="83" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>0.38142857142857145</v>
       </c>
@@ -5793,18 +6042,21 @@
       <c r="O83">
         <v>1</v>
       </c>
-      <c r="P83" t="s">
+      <c r="P83">
+        <v>1</v>
+      </c>
+      <c r="Q83" t="s">
         <v>182</v>
       </c>
-      <c r="Q83" t="s">
+      <c r="R83" t="s">
         <v>183</v>
       </c>
-      <c r="R83">
+      <c r="S83">
         <v>0.78988285714285722</v>
       </c>
-      <c r="S83" s="2"/>
-    </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T83" s="2"/>
+    </row>
+    <row r="84" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>0.48799999999999999</v>
       </c>
@@ -5850,18 +6102,21 @@
       <c r="O84">
         <v>1</v>
       </c>
-      <c r="P84" t="s">
+      <c r="P84">
+        <v>0</v>
+      </c>
+      <c r="Q84" t="s">
         <v>185</v>
       </c>
-      <c r="Q84" t="s">
+      <c r="R84" t="s">
         <v>186</v>
       </c>
-      <c r="R84">
+      <c r="S84">
         <v>0.63719999999999999</v>
       </c>
-      <c r="S84" s="2"/>
-    </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T84" s="2"/>
+    </row>
+    <row r="85" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>0.35966071428570956</v>
       </c>
@@ -5907,18 +6162,21 @@
       <c r="O85">
         <v>1</v>
       </c>
-      <c r="P85" t="s">
+      <c r="P85">
+        <v>1</v>
+      </c>
+      <c r="Q85" t="s">
         <v>188</v>
       </c>
-      <c r="Q85" t="s">
+      <c r="R85" t="s">
         <v>189</v>
       </c>
-      <c r="R85">
+      <c r="S85">
         <v>0.66415449999999998</v>
       </c>
-      <c r="S85" s="2"/>
-    </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T85" s="2"/>
+    </row>
+    <row r="86" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>0.87802499999999994</v>
       </c>
@@ -5964,18 +6222,21 @@
       <c r="O86">
         <v>1</v>
       </c>
-      <c r="P86" t="s">
+      <c r="P86">
+        <v>1</v>
+      </c>
+      <c r="Q86" t="s">
         <v>191</v>
       </c>
-      <c r="Q86" t="s">
+      <c r="R86" t="s">
         <v>189</v>
       </c>
-      <c r="R86">
+      <c r="S86">
         <v>0.64955249999999998</v>
       </c>
-      <c r="S86" s="2"/>
-    </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T86" s="2"/>
+    </row>
+    <row r="87" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>0.26663749999999992</v>
       </c>
@@ -6021,18 +6282,21 @@
       <c r="O87">
         <v>1</v>
       </c>
-      <c r="P87" t="s">
+      <c r="P87">
+        <v>1</v>
+      </c>
+      <c r="Q87" t="s">
         <v>193</v>
       </c>
-      <c r="Q87" t="s">
+      <c r="R87" t="s">
         <v>189</v>
       </c>
-      <c r="R87">
+      <c r="S87">
         <v>0.65847499999999992</v>
       </c>
-      <c r="S87" s="2"/>
-    </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T87" s="2"/>
+    </row>
+    <row r="88" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>0.92300000000000004</v>
       </c>
@@ -6078,18 +6342,21 @@
       <c r="O88">
         <v>1</v>
       </c>
-      <c r="P88" t="s">
+      <c r="P88">
+        <v>1</v>
+      </c>
+      <c r="Q88" t="s">
         <v>195</v>
       </c>
-      <c r="Q88" t="s">
+      <c r="R88" t="s">
         <v>189</v>
       </c>
-      <c r="R88">
+      <c r="S88">
         <v>0.95086914999999994</v>
       </c>
-      <c r="S88" s="2"/>
-    </row>
-    <row r="89" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T88" s="2"/>
+    </row>
+    <row r="89" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>0.66439999999999999</v>
       </c>
@@ -6135,18 +6402,21 @@
       <c r="O89">
         <v>1</v>
       </c>
-      <c r="P89" t="s">
+      <c r="P89">
+        <v>1</v>
+      </c>
+      <c r="Q89" t="s">
         <v>197</v>
       </c>
-      <c r="Q89" t="s">
+      <c r="R89" t="s">
         <v>189</v>
       </c>
-      <c r="R89">
+      <c r="S89">
         <v>0.83400000000000007</v>
       </c>
-      <c r="S89" s="2"/>
-    </row>
-    <row r="90" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T89" s="2"/>
+    </row>
+    <row r="90" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>6.7408685148545922E-2</v>
       </c>
@@ -6192,18 +6462,21 @@
       <c r="O90">
         <v>1</v>
       </c>
-      <c r="P90" t="s">
+      <c r="P90">
+        <v>1</v>
+      </c>
+      <c r="Q90" t="s">
         <v>199</v>
       </c>
-      <c r="Q90" t="s">
+      <c r="R90" t="s">
         <v>189</v>
       </c>
-      <c r="R90">
+      <c r="S90">
         <v>0.69163142857142856</v>
       </c>
-      <c r="S90" s="2"/>
-    </row>
-    <row r="91" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T90" s="2"/>
+    </row>
+    <row r="91" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>0.98219999999999996</v>
       </c>
@@ -6249,18 +6522,21 @@
       <c r="O91">
         <v>1</v>
       </c>
-      <c r="P91" t="s">
+      <c r="P91">
+        <v>1</v>
+      </c>
+      <c r="Q91" t="s">
         <v>201</v>
       </c>
-      <c r="Q91" t="s">
+      <c r="R91" t="s">
         <v>189</v>
       </c>
-      <c r="R91">
+      <c r="S91">
         <v>0.42</v>
       </c>
-      <c r="S91" s="2"/>
-    </row>
-    <row r="92" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T91" s="2"/>
+    </row>
+    <row r="92" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>0.16042857142857139</v>
       </c>
@@ -6306,18 +6582,21 @@
       <c r="O92">
         <v>1</v>
       </c>
-      <c r="P92" t="s">
+      <c r="P92">
+        <v>1</v>
+      </c>
+      <c r="Q92" t="s">
         <v>203</v>
       </c>
-      <c r="Q92" t="s">
+      <c r="R92" t="s">
         <v>189</v>
       </c>
-      <c r="R92">
+      <c r="S92">
         <v>0.64405000000000001</v>
       </c>
-      <c r="S92" s="2"/>
-    </row>
-    <row r="93" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T92" s="2"/>
+    </row>
+    <row r="93" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>0.52329999999999999</v>
       </c>
@@ -6363,18 +6642,21 @@
       <c r="O93">
         <v>1</v>
       </c>
-      <c r="P93" t="s">
+      <c r="P93">
+        <v>0</v>
+      </c>
+      <c r="Q93" t="s">
         <v>205</v>
       </c>
-      <c r="Q93" t="s">
+      <c r="R93" t="s">
         <v>189</v>
       </c>
-      <c r="R93">
+      <c r="S93">
         <v>0.62446299999999999</v>
       </c>
-      <c r="S93" s="2"/>
-    </row>
-    <row r="94" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T93" s="2"/>
+    </row>
+    <row r="94" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>0.18374166666666666</v>
       </c>
@@ -6420,18 +6702,21 @@
       <c r="O94">
         <v>0</v>
       </c>
-      <c r="P94" t="s">
+      <c r="P94">
+        <v>0</v>
+      </c>
+      <c r="Q94" t="s">
         <v>207</v>
       </c>
-      <c r="Q94" t="s">
+      <c r="R94" t="s">
         <v>208</v>
       </c>
-      <c r="R94">
+      <c r="S94">
         <v>0.41666666666666669</v>
       </c>
-      <c r="S94" s="2"/>
-    </row>
-    <row r="95" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T94" s="2"/>
+    </row>
+    <row r="95" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>0.27940000000000004</v>
       </c>
@@ -6477,18 +6762,21 @@
       <c r="O95">
         <v>1</v>
       </c>
-      <c r="P95" t="s">
+      <c r="P95">
+        <v>0</v>
+      </c>
+      <c r="Q95" t="s">
         <v>210</v>
       </c>
-      <c r="Q95" t="s">
+      <c r="R95" t="s">
         <v>208</v>
       </c>
-      <c r="R95">
+      <c r="S95">
         <v>0.36599999999999999</v>
       </c>
-      <c r="S95" s="2"/>
-    </row>
-    <row r="96" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T95" s="2"/>
+    </row>
+    <row r="96" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>0.43557725574925688</v>
       </c>
@@ -6534,18 +6822,21 @@
       <c r="O96">
         <v>1</v>
       </c>
-      <c r="P96" t="s">
+      <c r="P96">
+        <v>0</v>
+      </c>
+      <c r="Q96" t="s">
         <v>212</v>
       </c>
-      <c r="Q96" t="s">
+      <c r="R96" t="s">
         <v>208</v>
       </c>
-      <c r="R96">
+      <c r="S96">
         <v>0.47259729926478578</v>
       </c>
-      <c r="S96" s="2"/>
-    </row>
-    <row r="97" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T96" s="2"/>
+    </row>
+    <row r="97" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>0.52316666666666667</v>
       </c>
@@ -6591,18 +6882,21 @@
       <c r="O97">
         <v>1</v>
       </c>
-      <c r="P97" t="s">
+      <c r="P97">
+        <v>0</v>
+      </c>
+      <c r="Q97" t="s">
         <v>214</v>
       </c>
-      <c r="Q97" t="s">
+      <c r="R97" t="s">
         <v>208</v>
       </c>
-      <c r="R97">
+      <c r="S97">
         <v>0.61558499999999994</v>
       </c>
-      <c r="S97" s="2"/>
-    </row>
-    <row r="98" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T97" s="2"/>
+    </row>
+    <row r="98" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>0.284995</v>
       </c>
@@ -6648,18 +6942,21 @@
       <c r="O98">
         <v>1</v>
       </c>
-      <c r="P98" t="s">
+      <c r="P98">
+        <v>0</v>
+      </c>
+      <c r="Q98" t="s">
         <v>216</v>
       </c>
-      <c r="Q98" t="s">
+      <c r="R98" t="s">
         <v>208</v>
       </c>
-      <c r="R98">
+      <c r="S98">
         <v>0.29255549999999997</v>
       </c>
-      <c r="S98" s="2"/>
-    </row>
-    <row r="99" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T98" s="2"/>
+    </row>
+    <row r="99" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>0.66449999999999998</v>
       </c>
@@ -6705,24 +7002,36 @@
       <c r="O99">
         <v>0</v>
       </c>
-      <c r="P99" t="s">
+      <c r="P99">
+        <v>0</v>
+      </c>
+      <c r="Q99" t="s">
         <v>218</v>
       </c>
-      <c r="Q99" t="s">
+      <c r="R99" t="s">
         <v>208</v>
       </c>
-      <c r="R99">
+      <c r="S99">
         <v>0.625</v>
       </c>
-      <c r="S99" s="2"/>
+      <c r="T99" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R99" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:S99" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006D48397D13837C43B684B08DAD64BF8C" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="aa6028da15d92db9b6aceca8d55fbe9d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="0360f195-d042-45e7-aa5c-1d93fc6d8805" xmlns:ns3="2c1232c3-bf45-45cd-a7a3-d01a7b037b08" xmlns:ns4="985ec44e-1bab-4c0b-9df0-6ba128686fc9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4e7b2f341d84b3532902f1b94e65ae39" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="0360f195-d042-45e7-aa5c-1d93fc6d8805"/>
@@ -6982,16 +7291,15 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE86C94B-ECA9-49A3-8796-801BE3073E71}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A29F113F-D23E-4E8A-ABA5-151D4336A474}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7011,14 +7319,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE86C94B-ECA9-49A3-8796-801BE3073E71}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{8b77875e-5908-45a0-9cb4-dec9ae074618}" enabled="1" method="Privileged" siteId="{0f9e35db-544f-4f60-bdcc-5ea416e6dc70}" contentBits="0" removed="0"/>

--- a/Templates/raw_indicators.xlsx
+++ b/Templates/raw_indicators.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aa4c1864c6ba7ffe/Apps/Policy Priority Inference/Templates/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\Antigravity\Policy Priority Inference\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{1D17FAE4-2E6B-4B31-92F1-151F6B8AEFE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C9EEDAD-30E6-41C9-A5CF-7B030E07BDFF}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{094A4F28-1D01-4BE5-9CE2-4D0F337AD6C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="221">
   <si>
     <t>seriesCode</t>
   </si>
@@ -696,6 +696,9 @@
   </si>
   <si>
     <t>Invert</t>
+  </si>
+  <si>
+    <t/>
   </si>
 </sst>
 </file>
@@ -1137,8 +1140,8 @@
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>0.64694444444444343</v>
+      <c r="A2" t="s">
+        <v>220</v>
       </c>
       <c r="B2">
         <v>0.60933333333333339</v>
@@ -1197,11 +1200,11 @@
       <c r="T2" s="2"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>0.29557142857142793</v>
-      </c>
-      <c r="B3">
-        <v>0.31149999999999523</v>
+      <c r="A3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B3" t="s">
+        <v>220</v>
       </c>
       <c r="C3">
         <v>0.32199999999999995</v>
@@ -1224,8 +1227,8 @@
       <c r="I3">
         <v>0.47499999999999998</v>
       </c>
-      <c r="J3">
-        <v>0.43892857142856911</v>
+      <c r="J3" t="s">
+        <v>220</v>
       </c>
       <c r="K3" t="s">
         <v>11</v>
@@ -1257,8 +1260,8 @@
       <c r="T3" s="2"/>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>0.30203888888888741</v>
+      <c r="A4" t="s">
+        <v>220</v>
       </c>
       <c r="B4">
         <v>0.30379999999999996</v>
@@ -1317,8 +1320,8 @@
       <c r="T4" s="2"/>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>0.32489444444445326</v>
+      <c r="A5" t="s">
+        <v>220</v>
       </c>
       <c r="B5">
         <v>0.33819999999999995</v>
@@ -1377,8 +1380,8 @@
       <c r="T5" s="2"/>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>0.68939999999999912</v>
+      <c r="A6" t="s">
+        <v>220</v>
       </c>
       <c r="B6">
         <v>0.69900000000000007</v>
@@ -1464,8 +1467,8 @@
       <c r="I7">
         <v>0.58200000000000007</v>
       </c>
-      <c r="J7">
-        <v>0.59186944444444478</v>
+      <c r="J7" t="s">
+        <v>220</v>
       </c>
       <c r="K7" t="s">
         <v>19</v>
@@ -1518,14 +1521,14 @@
       <c r="G8">
         <v>0.56000000000000005</v>
       </c>
-      <c r="H8">
-        <v>0.56828571428571273</v>
-      </c>
-      <c r="I8">
-        <v>0.57549999999999812</v>
-      </c>
-      <c r="J8">
-        <v>0.5827142857142853</v>
+      <c r="H8" t="s">
+        <v>220</v>
+      </c>
+      <c r="I8" t="s">
+        <v>220</v>
+      </c>
+      <c r="J8" t="s">
+        <v>220</v>
       </c>
       <c r="K8" t="s">
         <v>21</v>
@@ -1584,8 +1587,8 @@
       <c r="I9">
         <v>0.88700000000000001</v>
       </c>
-      <c r="J9">
-        <v>0.87165833333333387</v>
+      <c r="J9" t="s">
+        <v>220</v>
       </c>
       <c r="K9" t="s">
         <v>24</v>
@@ -1824,8 +1827,8 @@
       <c r="I13">
         <v>0.875</v>
       </c>
-      <c r="J13">
-        <v>0.88463888888888675</v>
+      <c r="J13" t="s">
+        <v>220</v>
       </c>
       <c r="K13" t="s">
         <v>33</v>
@@ -2124,8 +2127,8 @@
       <c r="I18">
         <v>0.6875</v>
       </c>
-      <c r="J18">
-        <v>0.68844444444444441</v>
+      <c r="J18" t="s">
+        <v>220</v>
       </c>
       <c r="K18" t="s">
         <v>43</v>
@@ -2217,8 +2220,8 @@
       <c r="T19" s="2"/>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>0.50249537037036873</v>
+      <c r="A20" t="s">
+        <v>220</v>
       </c>
       <c r="B20">
         <v>0.48416666666666669</v>
@@ -2397,8 +2400,8 @@
       <c r="T22" s="3"/>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>0.7998412698412698</v>
+      <c r="A23" t="s">
+        <v>220</v>
       </c>
       <c r="B23">
         <v>0.79428571428571426</v>
@@ -2457,8 +2460,8 @@
       <c r="T23" s="2"/>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>0.67923076923077019</v>
+      <c r="A24" t="s">
+        <v>220</v>
       </c>
       <c r="B24">
         <v>0.69000000000000006</v>
@@ -2544,8 +2547,8 @@
       <c r="I25">
         <v>0.44130000000000003</v>
       </c>
-      <c r="J25">
-        <v>0.36526111111110993</v>
+      <c r="J25" t="s">
+        <v>220</v>
       </c>
       <c r="K25" t="s">
         <v>58</v>
@@ -2817,8 +2820,8 @@
       <c r="T29" s="2"/>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>0.46566666666666379</v>
+      <c r="A30" t="s">
+        <v>220</v>
       </c>
       <c r="B30">
         <v>0.46600000000000003</v>
@@ -2877,8 +2880,8 @@
       <c r="T30" s="2"/>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>0.21902777777777871</v>
+      <c r="A31" t="s">
+        <v>220</v>
       </c>
       <c r="B31">
         <v>0.21100000000000002</v>
@@ -2937,8 +2940,8 @@
       <c r="T31" s="2"/>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>0.95871428571428585</v>
+      <c r="A32" t="s">
+        <v>220</v>
       </c>
       <c r="B32">
         <v>0.95400000000000007</v>
@@ -2964,8 +2967,8 @@
       <c r="I32">
         <v>0.96</v>
       </c>
-      <c r="J32">
-        <v>0.9522857142857144</v>
+      <c r="J32" t="s">
+        <v>220</v>
       </c>
       <c r="K32" t="s">
         <v>72</v>
@@ -2997,8 +3000,8 @@
       <c r="T32" s="2"/>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>0.92099999999999937</v>
+      <c r="A33" t="s">
+        <v>220</v>
       </c>
       <c r="B33">
         <v>0.9</v>
@@ -3024,8 +3027,8 @@
       <c r="I33">
         <v>0.91200000000000003</v>
       </c>
-      <c r="J33">
-        <v>0.90299999999999958</v>
+      <c r="J33" t="s">
+        <v>220</v>
       </c>
       <c r="K33" t="s">
         <v>74</v>
@@ -3237,14 +3240,14 @@
       <c r="T36" s="2"/>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <v>0.20585714285714474</v>
-      </c>
-      <c r="B37">
-        <v>0.21678571428571658</v>
-      </c>
-      <c r="C37">
-        <v>0.22771428571428842</v>
+      <c r="A37" t="s">
+        <v>220</v>
+      </c>
+      <c r="B37" t="s">
+        <v>220</v>
+      </c>
+      <c r="C37" t="s">
+        <v>220</v>
       </c>
       <c r="D37">
         <v>0.20399999999999999</v>
@@ -3444,8 +3447,8 @@
       <c r="I40">
         <v>0.62</v>
       </c>
-      <c r="J40">
-        <v>0.62333333333333485</v>
+      <c r="J40" t="s">
+        <v>220</v>
       </c>
       <c r="K40" t="s">
         <v>88</v>
@@ -3678,14 +3681,14 @@
       <c r="G44">
         <v>0.74400000000000011</v>
       </c>
-      <c r="H44">
-        <v>0.74457142857142866</v>
-      </c>
-      <c r="I44">
-        <v>0.7475000000000005</v>
-      </c>
-      <c r="J44">
-        <v>0.75042857142857144</v>
+      <c r="H44" t="s">
+        <v>220</v>
+      </c>
+      <c r="I44" t="s">
+        <v>220</v>
+      </c>
+      <c r="J44" t="s">
+        <v>220</v>
       </c>
       <c r="K44" t="s">
         <v>96</v>
@@ -3897,8 +3900,8 @@
       <c r="T47" s="2"/>
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A48">
-        <v>0.62437222222222388</v>
+      <c r="A48" t="s">
+        <v>220</v>
       </c>
       <c r="B48">
         <v>0.60709999999999997</v>
@@ -4077,8 +4080,8 @@
       <c r="T50" s="2"/>
     </row>
     <row r="51" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A51">
-        <v>0.24871944444444472</v>
+      <c r="A51" t="s">
+        <v>220</v>
       </c>
       <c r="B51">
         <v>0.252</v>
@@ -4198,34 +4201,34 @@
     </row>
     <row r="53" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>0.32999999999999996</v>
+        <v>0.16440000000000002</v>
       </c>
       <c r="B53">
-        <v>0.29000000000000004</v>
+        <v>0.25219999999999998</v>
       </c>
       <c r="C53">
-        <v>0.41000000000000003</v>
+        <v>0.3448</v>
       </c>
       <c r="D53">
-        <v>0.30000000000000004</v>
+        <v>0.32840000000000003</v>
       </c>
       <c r="E53">
-        <v>0.27</v>
+        <v>0.25379999999999997</v>
       </c>
       <c r="F53">
-        <v>0.39</v>
+        <v>0.30760000000000004</v>
       </c>
       <c r="G53">
-        <v>0.42000000000000004</v>
+        <v>0.32200000000000001</v>
       </c>
       <c r="H53">
-        <v>0.41000000000000003</v>
+        <v>0.3236</v>
       </c>
       <c r="I53">
-        <v>0.35</v>
+        <v>0.30640000000000001</v>
       </c>
       <c r="J53">
-        <v>0.39805555555555827</v>
+        <v>0.33360000000000001</v>
       </c>
       <c r="K53" t="s">
         <v>116</v>
@@ -4258,34 +4261,34 @@
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>0.16440000000000002</v>
+        <v>0.32999999999999996</v>
       </c>
       <c r="B54">
-        <v>0.25219999999999998</v>
+        <v>0.29000000000000004</v>
       </c>
       <c r="C54">
-        <v>0.3448</v>
+        <v>0.41000000000000003</v>
       </c>
       <c r="D54">
-        <v>0.32840000000000003</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="E54">
-        <v>0.25379999999999997</v>
+        <v>0.27</v>
       </c>
       <c r="F54">
-        <v>0.30760000000000004</v>
+        <v>0.39</v>
       </c>
       <c r="G54">
-        <v>0.32200000000000001</v>
+        <v>0.42000000000000004</v>
       </c>
       <c r="H54">
-        <v>0.3236</v>
+        <v>0.41000000000000003</v>
       </c>
       <c r="I54">
-        <v>0.30640000000000001</v>
-      </c>
-      <c r="J54">
-        <v>0.33360000000000001</v>
+        <v>0.35</v>
+      </c>
+      <c r="J54" t="s">
+        <v>220</v>
       </c>
       <c r="K54" t="s">
         <v>119</v>
@@ -4404,8 +4407,8 @@
       <c r="I56">
         <v>0.62634444444444448</v>
       </c>
-      <c r="J56">
-        <v>0.61006188271605311</v>
+      <c r="J56" t="s">
+        <v>220</v>
       </c>
       <c r="K56" t="s">
         <v>123</v>
@@ -4461,11 +4464,11 @@
       <c r="H57">
         <v>0.81252333333333338</v>
       </c>
-      <c r="I57">
-        <v>0.90117285714285345</v>
-      </c>
-      <c r="J57">
-        <v>0.93659682539683331</v>
+      <c r="I57" t="s">
+        <v>220</v>
+      </c>
+      <c r="J57" t="s">
+        <v>220</v>
       </c>
       <c r="K57" t="s">
         <v>126</v>
@@ -4617,8 +4620,8 @@
       <c r="T59" s="2"/>
     </row>
     <row r="60" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A60">
-        <v>0.56781666666666664</v>
+      <c r="A60" t="s">
+        <v>220</v>
       </c>
       <c r="B60">
         <v>0.57889999999999997</v>
@@ -4677,8 +4680,8 @@
       <c r="T60" s="2"/>
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A61">
-        <v>0.50106666666666677</v>
+      <c r="A61" t="s">
+        <v>220</v>
       </c>
       <c r="B61">
         <v>0.50039999999999996</v>
@@ -4737,8 +4740,8 @@
       <c r="T61" s="2"/>
     </row>
     <row r="62" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A62">
-        <v>0.68063888888888791</v>
+      <c r="A62" t="s">
+        <v>220</v>
       </c>
       <c r="B62">
         <v>0.67120000000000002</v>
@@ -4797,8 +4800,8 @@
       <c r="T62" s="2"/>
     </row>
     <row r="63" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A63">
-        <v>0.83863268581406469</v>
+      <c r="A63" t="s">
+        <v>220</v>
       </c>
       <c r="B63">
         <v>0.8375154011141358</v>
@@ -4917,8 +4920,8 @@
       <c r="T64" s="2"/>
     </row>
     <row r="65" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A65">
-        <v>0.43671944444444399</v>
+      <c r="A65" t="s">
+        <v>220</v>
       </c>
       <c r="B65">
         <v>0.43799999999999994</v>
@@ -4977,8 +4980,8 @@
       <c r="T65" s="2"/>
     </row>
     <row r="66" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A66">
-        <v>0.74588611111111114</v>
+      <c r="A66" t="s">
+        <v>220</v>
       </c>
       <c r="B66">
         <v>0.74900000000000011</v>
@@ -5037,8 +5040,8 @@
       <c r="T66" s="2"/>
     </row>
     <row r="67" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A67">
-        <v>0.7713277777777785</v>
+      <c r="A67" t="s">
+        <v>220</v>
       </c>
       <c r="B67">
         <v>0.77890000000000004</v>
@@ -5124,8 +5127,8 @@
       <c r="I68">
         <v>0.503</v>
       </c>
-      <c r="J68">
-        <v>0.47288611111111223</v>
+      <c r="J68" t="s">
+        <v>220</v>
       </c>
       <c r="K68" t="s">
         <v>148</v>
@@ -5364,8 +5367,8 @@
       <c r="I72">
         <v>0.74739999999999995</v>
       </c>
-      <c r="J72">
-        <v>0.59260555555555783</v>
+      <c r="J72" t="s">
+        <v>220</v>
       </c>
       <c r="K72" t="s">
         <v>156</v>
@@ -5697,8 +5700,8 @@
       <c r="T77" s="3"/>
     </row>
     <row r="78" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A78">
-        <v>0.366458333333334</v>
+      <c r="A78" t="s">
+        <v>220</v>
       </c>
       <c r="B78">
         <v>0.43</v>
@@ -5757,8 +5760,8 @@
       <c r="T78" s="2"/>
     </row>
     <row r="79" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A79">
-        <v>0.43897222222222254</v>
+      <c r="A79" t="s">
+        <v>220</v>
       </c>
       <c r="B79">
         <v>0.49850000000000005</v>
@@ -5817,14 +5820,14 @@
       <c r="T79" s="2"/>
     </row>
     <row r="80" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A80">
-        <v>0.52628571428571469</v>
-      </c>
-      <c r="B80">
-        <v>0.53407142857142986</v>
-      </c>
-      <c r="C80">
-        <v>0.54185714285714326</v>
+      <c r="A80" t="s">
+        <v>220</v>
+      </c>
+      <c r="B80" t="s">
+        <v>220</v>
+      </c>
+      <c r="C80" t="s">
+        <v>220</v>
       </c>
       <c r="D80">
         <v>0.58299999999999996</v>
@@ -6117,8 +6120,8 @@
       <c r="T84" s="2"/>
     </row>
     <row r="85" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A85">
-        <v>0.35966071428570956</v>
+      <c r="A85" t="s">
+        <v>220</v>
       </c>
       <c r="B85">
         <v>0.48250000000000004</v>
@@ -6144,8 +6147,8 @@
       <c r="I85">
         <v>0.54349999999999998</v>
       </c>
-      <c r="J85">
-        <v>0.51196428571428498</v>
+      <c r="J85" t="s">
+        <v>220</v>
       </c>
       <c r="K85" t="s">
         <v>187</v>
@@ -6418,34 +6421,34 @@
     </row>
     <row r="90" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>6.7408685148545922E-2</v>
+        <v>0.16042857142857139</v>
       </c>
       <c r="B90">
-        <v>8.1432452212469447E-2</v>
+        <v>0.22657142857142856</v>
       </c>
       <c r="C90">
-        <v>9.8373737133769984E-2</v>
+        <v>0.16128571428571428</v>
       </c>
       <c r="D90">
-        <v>0.16510000000000005</v>
+        <v>0.14485714285714288</v>
       </c>
       <c r="E90">
-        <v>0.12269999999999996</v>
+        <v>0.36071428571428571</v>
       </c>
       <c r="F90">
-        <v>0.14370000000000005</v>
+        <v>0.47357142857142853</v>
       </c>
       <c r="G90">
-        <v>0.13980000000000004</v>
+        <v>0.53157142857142858</v>
       </c>
       <c r="H90">
-        <v>0.35639999999999999</v>
+        <v>0.44742857142857145</v>
       </c>
       <c r="I90">
-        <v>0.33150000000000007</v>
-      </c>
-      <c r="J90">
-        <v>0.3669</v>
+        <v>0.55600000000000005</v>
+      </c>
+      <c r="J90" t="s">
+        <v>220</v>
       </c>
       <c r="K90" t="s">
         <v>198</v>
@@ -6477,35 +6480,35 @@
       <c r="T90" s="2"/>
     </row>
     <row r="91" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A91">
-        <v>0.98219999999999996</v>
-      </c>
-      <c r="B91">
-        <v>0.98240000000000005</v>
-      </c>
-      <c r="C91">
-        <v>0.85824999999999996</v>
+      <c r="A91" t="s">
+        <v>220</v>
+      </c>
+      <c r="B91" t="s">
+        <v>220</v>
+      </c>
+      <c r="C91" t="s">
+        <v>220</v>
       </c>
       <c r="D91">
-        <v>0.79990000000000006</v>
+        <v>0.16510000000000005</v>
       </c>
       <c r="E91">
-        <v>0.71209999999999996</v>
+        <v>0.12269999999999996</v>
       </c>
       <c r="F91">
-        <v>0.78344999999999998</v>
+        <v>0.14370000000000005</v>
       </c>
       <c r="G91">
-        <v>0.71319999999999995</v>
+        <v>0.13980000000000004</v>
       </c>
       <c r="H91">
-        <v>0.58350000000000002</v>
+        <v>0.35639999999999999</v>
       </c>
       <c r="I91">
-        <v>0.49149999999999999</v>
+        <v>0.33150000000000007</v>
       </c>
       <c r="J91">
-        <v>0.4785513888888886</v>
+        <v>0.3669</v>
       </c>
       <c r="K91" t="s">
         <v>200</v>
@@ -6538,34 +6541,34 @@
     </row>
     <row r="92" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>0.16042857142857139</v>
+        <v>0.98219999999999996</v>
       </c>
       <c r="B92">
-        <v>0.22657142857142856</v>
+        <v>0.98240000000000005</v>
       </c>
       <c r="C92">
-        <v>0.16128571428571428</v>
+        <v>0.85824999999999996</v>
       </c>
       <c r="D92">
-        <v>0.14485714285714288</v>
+        <v>0.79990000000000006</v>
       </c>
       <c r="E92">
-        <v>0.36071428571428571</v>
+        <v>0.71209999999999996</v>
       </c>
       <c r="F92">
-        <v>0.47357142857142853</v>
+        <v>0.78344999999999998</v>
       </c>
       <c r="G92">
-        <v>0.53157142857142858</v>
+        <v>0.71319999999999995</v>
       </c>
       <c r="H92">
-        <v>0.44742857142857145</v>
+        <v>0.58350000000000002</v>
       </c>
       <c r="I92">
-        <v>0.55600000000000005</v>
-      </c>
-      <c r="J92">
-        <v>0.61644841269841777</v>
+        <v>0.49149999999999999</v>
+      </c>
+      <c r="J92" t="s">
+        <v>220</v>
       </c>
       <c r="K92" t="s">
         <v>202</v>
@@ -6804,8 +6807,8 @@
       <c r="I96">
         <v>0.45099999999999996</v>
       </c>
-      <c r="J96">
-        <v>0.46894882084098022</v>
+      <c r="J96" t="s">
+        <v>220</v>
       </c>
       <c r="K96" t="s">
         <v>211</v>
@@ -6864,8 +6867,8 @@
       <c r="I97">
         <v>0.47599999999999998</v>
       </c>
-      <c r="J97">
-        <v>0.53918981481481509</v>
+      <c r="J97" t="s">
+        <v>220</v>
       </c>
       <c r="K97" t="s">
         <v>213</v>
@@ -7023,15 +7026,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006D48397D13837C43B684B08DAD64BF8C" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="aa6028da15d92db9b6aceca8d55fbe9d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="0360f195-d042-45e7-aa5c-1d93fc6d8805" xmlns:ns3="2c1232c3-bf45-45cd-a7a3-d01a7b037b08" xmlns:ns4="985ec44e-1bab-4c0b-9df0-6ba128686fc9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4e7b2f341d84b3532902f1b94e65ae39" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="0360f195-d042-45e7-aa5c-1d93fc6d8805"/>
@@ -7291,15 +7285,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE86C94B-ECA9-49A3-8796-801BE3073E71}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A29F113F-D23E-4E8A-ABA5-151D4336A474}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7319,6 +7314,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE86C94B-ECA9-49A3-8796-801BE3073E71}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{8b77875e-5908-45a0-9cb4-dec9ae074618}" enabled="1" method="Privileged" siteId="{0f9e35db-544f-4f60-bdcc-5ea416e6dc70}" contentBits="0" removed="0"/>
